--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126348492</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126348506</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126348507</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126348492</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126348506</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>126348507</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348492</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348506</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348507</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126348492</v>
+        <v>135784658</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>92048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412415</v>
+        <v>412396</v>
       </c>
       <c r="R2" t="n">
-        <v>6966371</v>
+        <v>6966324</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,62 +765,62 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348492</t>
+          <t>https://artportalen.se/Sighting/135784658</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126348506</v>
+        <v>135784650</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412375</v>
+        <v>412364</v>
       </c>
       <c r="R3" t="n">
-        <v>6966295</v>
+        <v>6966349</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,27 +867,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126348506</t>
+          <t>https://artportalen.se/Sighting/135784650</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126348507</v>
+        <v>135784655</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>78844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Digerberget, Hjd</t>
+          <t>Putten, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412391</v>
+        <v>412389</v>
       </c>
       <c r="R4" t="n">
-        <v>6966325</v>
+        <v>6966289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,17 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,18 +969,951 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135784655</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135784651</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>412364</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6966349</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784651</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135784653</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>412359</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6966319</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784653</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126348492</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>412415</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6966371</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348492</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126348506</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>412375</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6966295</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348506</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126348507</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Digerberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>412391</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6966325</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/126348507</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135784652</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>412369</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6966348</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784652</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135784654</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>412359</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6966324</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784654</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135784659</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>412390</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6966336</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784659</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135784656</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Putten, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>412402</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6966280</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784656</t>
         </is>
       </c>
     </row>
@@ -1004,6 +1922,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784658</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784658</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784650</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784655</v>
       </c>
       <c r="B4" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784651</v>
       </c>
       <c r="B5" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784653</v>
       </c>
       <c r="B6" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135784654</v>
       </c>
       <c r="B11" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>135784659</v>
       </c>
       <c r="B12" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135784656</v>
       </c>
       <c r="B13" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784658</v>
       </c>
       <c r="B2" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784650</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784655</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784651</v>
       </c>
       <c r="B5" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784653</v>
       </c>
       <c r="B6" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135784654</v>
       </c>
       <c r="B11" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>135784659</v>
       </c>
       <c r="B12" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135784656</v>
       </c>
       <c r="B13" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784658</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784658</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784650</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784655</v>
       </c>
       <c r="B4" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784651</v>
       </c>
       <c r="B5" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784653</v>
       </c>
       <c r="B6" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135784654</v>
       </c>
       <c r="B11" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>135784659</v>
       </c>
       <c r="B12" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135784656</v>
       </c>
       <c r="B13" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784658</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784650</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784655</v>
       </c>
       <c r="B4" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784651</v>
       </c>
       <c r="B5" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784653</v>
       </c>
       <c r="B6" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135784654</v>
       </c>
       <c r="B11" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>135784659</v>
       </c>
       <c r="B12" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135784656</v>
       </c>
       <c r="B13" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784658</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784650</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784655</v>
       </c>
       <c r="B4" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784651</v>
       </c>
       <c r="B5" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784653</v>
       </c>
       <c r="B6" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135784654</v>
       </c>
       <c r="B11" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>135784659</v>
       </c>
       <c r="B12" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135784656</v>
       </c>
       <c r="B13" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784658</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784650</v>
       </c>
       <c r="B3" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784655</v>
       </c>
       <c r="B4" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784651</v>
       </c>
       <c r="B5" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784653</v>
       </c>
       <c r="B6" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135784654</v>
       </c>
       <c r="B11" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>135784659</v>
       </c>
       <c r="B12" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135784656</v>
       </c>
       <c r="B13" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784658</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784650</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784655</v>
       </c>
       <c r="B4" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784651</v>
       </c>
       <c r="B5" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784653</v>
       </c>
       <c r="B6" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135784654</v>
       </c>
       <c r="B11" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>135784659</v>
       </c>
       <c r="B12" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135784656</v>
       </c>
       <c r="B13" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 21632-2025 artfynd.xlsx
+++ b/artfynd/A 21632-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784658</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135784652</v>
       </c>
       <c r="B10" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
